--- a/90minutersdata/Player/2026/langpass-genomskarare.xlsx
+++ b/90minutersdata/Player/2026/langpass-genomskarare.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>LåP</t>
+          <t>LÃ¥P</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -498,7 +498,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F. AdjeiF. Adjei</t>
+          <t>G. WallentinG. Wallentin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -506,23 +506,23 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="F3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
       <c r="H3" t="n">
-        <v>1800</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. WallentinG. Wallentin</t>
+          <t>D. StenssonD. Stensson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -530,23 +530,23 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1763</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Stryger LarsenJ. Stryger Larsen</t>
+          <t>J. TagessonJ. Tagesson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -570,7 +570,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. PikkarainenJ. Pikkarainen</t>
+          <t>K. HolmÃ©nK. HolmÃ©n</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -578,23 +578,23 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>1440</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>K. HolménK. Holmén</t>
+          <t>N. Astrand JohnN. Astrand John</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -602,95 +602,95 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1326</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>N. Astrand JohnN. Astrand John</t>
+          <t>C. NildÃ©nC. NildÃ©n</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1313</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. CsongvaiA. Csongvai</t>
+          <t>F. OttossonF. Ottosson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>1113</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>N. MoroN. Moro</t>
+          <t>J. PikkarainenJ. Pikkarainen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>296</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>1102</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>O. KrusnellO. Krusnell</t>
+          <t>I. CamaraI. Camara</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -698,47 +698,47 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1080</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S. ØverbyS. Øverby</t>
+          <t>E. TougjasE. Tougjas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>290</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>1080</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A. TroelsenA. Troelsen</t>
+          <t>N. MoroN. Moro</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -746,71 +746,71 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1069</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C. NildénC. Nildén</t>
+          <t>S. ÃverbyS. Ãverby</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1000</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T. AnkerT. Anker</t>
+          <t>P. GregorP. Gregor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>990</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H. CastegrenH. Castegren</t>
+          <t>G. FribergG. Friberg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -818,112 +818,112 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>990</v>
+        <v>947</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stanley WilsonStanley Wilson</t>
+          <t>V. WernerssonV. Wernersson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>268</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>957</v>
+        <v>907</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A. DariA. Dari</t>
+          <t>BusanelloBusanello</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>947</v>
+        <v>896</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>J. LindbergJ. Lindberg</t>
+          <t>R. YeboahR. Yeboah</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>947</v>
+        <v>874</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M. RaffertyM. Rafferty</t>
+          <t>H. MagnussonH. Magnusson</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>68</v>
+        <v>275</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>926</v>
+        <v>851</v>
       </c>
     </row>
     <row r="21">
@@ -935,50 +935,50 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>923</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>V. WernerssonV. Wernersson</t>
+          <t>A. TroelsenA. Troelsen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>176</v>
+        <v>294</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>920</v>
+        <v>827</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>C. RöslerC. Rösler</t>
+          <t>H. Andersson MellaH. Andersson Mella</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -986,95 +986,95 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>918</v>
+        <v>818</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>E. StroudE. Stroud</t>
+          <t>A. CsongvaiA. Csongvai</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>194</v>
+        <v>269</v>
       </c>
       <c r="F24" t="n">
         <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>881</v>
+        <v>803</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R. FrejR. Frej</t>
+          <t>J. Stryger LarsenJ. Stryger Larsen</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>853</v>
+        <v>803</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>T. IsherwoodT. Isherwood</t>
+          <t>J. FagerjordJ. Fagerjord</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>822</v>
+        <v>790</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H. MagnussonH. Magnusson</t>
+          <t>B. HusseinB. Hussein</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1082,64 +1082,64 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>203</v>
+        <v>57</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>798</v>
+        <v>789</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>J. KarlssonJ. Karlsson</t>
+          <t>M. de BrienneM. de Brienne</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>783</v>
+        <v>788</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S. HakšabanovićS. Hakšabanović</t>
+          <t>R. WikstrÃ¶mR. WikstrÃ¶m</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
+        <v>298</v>
+      </c>
+      <c r="F29" t="n">
         <v>23</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="30">
@@ -1170,45 +1170,47 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>L. ThorellL. Thorell</t>
+          <t>L. SÃ¦traL. SÃ¦tra</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>47</v>
+        <v>225</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>766</v>
+        <v>760</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A. WängbergA. Wängberg</t>
+          <t>O. Ã+grenO. Ã+gren</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>758</v>
@@ -1218,216 +1220,216 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M. LarssonM. Larsson</t>
+          <t>O. ZandÃ©nO. ZandÃ©n</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>95</v>
+        <v>294</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>758</v>
+        <v>735</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>O. AdinduO. Adindu</t>
+          <t>T. HeintzT. Heintz</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>294</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>750</v>
+        <v>735</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>E. TougjasE. Tougjas</t>
+          <t>G. YiriyonG. Yiriyon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>742</v>
+        <v>730</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R. WikströmR. Wikström</t>
+          <t>T. IsherwoodT. Isherwood</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="F36" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M. RygaardM. Rygaard</t>
+          <t>E. StroudE. Stroud</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>62</v>
+        <v>289</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>726</v>
+        <v>716</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>J. FagerjordJ. Fagerjord</t>
+          <t>Stanley WilsonStanley Wilson</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>63</v>
+        <v>275</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>714</v>
+        <v>687</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>J. SimpsonJ. Simpson</t>
+          <t>A. NorÃ©nA. NorÃ©n</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>101</v>
+        <v>289</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>713</v>
+        <v>685</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>M. de BrienneM. de Brienne</t>
+          <t>T. AnkerT. Anker</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>76</v>
+        <v>294</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>711</v>
+        <v>673</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>O. Parker-PriceO. Parker-Price</t>
+          <t>R. FrejR. Frej</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>197</v>
+        <v>294</v>
       </c>
       <c r="F41" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G41" t="n">
         <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>685</v>
+        <v>673</v>
       </c>
     </row>
     <row r="42">
@@ -1458,127 +1460,127 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H. SkoglundH. Skoglund</t>
+          <t>A. DariA. Dari</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>95</v>
+        <v>272</v>
       </c>
       <c r="F43" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R. AsconeR. Ascone</t>
+          <t>J. SimpsonJ. Simpson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>649</v>
+        <v>658</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>V. EkströmV. Ekström</t>
+          <t>K. BusuladÅ¾iÄK. BusuladÅ¾iÄ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="F45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>630</v>
+        <v>655</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>O. ZandénO. Zandén</t>
+          <t>J. KarlssonJ. Karlsson</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="F46" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>624</v>
+        <v>647</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>G. YiriyonG. Yiriyon</t>
+          <t>H. CastegrenH. Castegren</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>90</v>
+        <v>294</v>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>600</v>
+        <v>643</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>F. OttossonF. Ottosson</t>
+          <t>J. LindbergJ. Lindberg</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1586,64 +1588,64 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>169</v>
+        <v>28</v>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>586</v>
+        <v>643</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>F. HelanderF. Helander</t>
+          <t>F. ErikssonF. Eriksson</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>201</v>
+        <v>294</v>
       </c>
       <c r="F49" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>582</v>
+        <v>612</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>J. HammarJ. Hammar</t>
+          <t>O. Parker-PriceO. Parker-Price</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>254</v>
+      </c>
+      <c r="F50" t="n">
+        <v>15</v>
+      </c>
+      <c r="G50" t="n">
         <v>2</v>
       </c>
-      <c r="E50" t="n">
-        <v>201</v>
-      </c>
-      <c r="F50" t="n">
-        <v>13</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
       <c r="H50" t="n">
-        <v>582</v>
+        <v>602</v>
       </c>
     </row>
     <row r="51">
@@ -1655,170 +1657,170 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>581</v>
+        <v>600</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>O. ÅgrenO. Ågren</t>
+          <t>F. AdjeiF. Adjei</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>568</v>
+        <v>600</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>F. WintherF. Winther</t>
+          <t>V. EkstrÃ¶mV. EkstrÃ¶m</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>568</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B. CelinaB. Celina</t>
+          <t>S. HolmÃ©nS. HolmÃ©n</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>563</v>
+        <v>590</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>K. BusuladžićK. Busuladžić</t>
+          <t>R. AsconeR. Ascone</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>33</v>
+        <v>290</v>
       </c>
       <c r="F55" t="n">
+        <v>17</v>
+      </c>
+      <c r="G55" t="n">
         <v>2</v>
       </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
       <c r="H55" t="n">
-        <v>545</v>
+        <v>590</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>T. MiettinenT. Miettinen</t>
+          <t>A. JallowA. Jallow</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>542</v>
+        <v>582</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>N. Girmai NetabayN. Girmai Netabay</t>
+          <t>D. SundgrenD. Sundgren</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>100</v>
+        <v>296</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B. LaturnusB. Laturnus</t>
+          <t>L. ThorellL. Thorell</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1826,23 +1828,23 @@
         <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>184</v>
+        <v>125</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>538</v>
+        <v>576</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R. JanssonR. Jansson</t>
+          <t>J. NilssonJ. Nilsson</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1850,160 +1852,160 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>529</v>
+        <v>563</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Z. RåvikZ. Råvik</t>
+          <t>J. HammarJ. Hammar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="F60" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>529</v>
+        <v>560</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A. KouameA. Kouame</t>
+          <t>A. ErlingmarkA. Erlingmark</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
+        <v>294</v>
+      </c>
+      <c r="F61" t="n">
         <v>17</v>
       </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>529</v>
+        <v>551</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A. MannehA. Manneh</t>
+          <t>M. RygaardM. Rygaard</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>510</v>
+        <v>540</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>F. ErikssonF. Eriksson</t>
+          <t>C. StyffeC. Styffe</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>285</v>
+      </c>
+      <c r="F63" t="n">
+        <v>15</v>
+      </c>
+      <c r="G63" t="n">
         <v>2</v>
       </c>
-      <c r="E63" t="n">
-        <v>196</v>
-      </c>
-      <c r="F63" t="n">
-        <v>11</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
       <c r="H63" t="n">
-        <v>505</v>
+        <v>537</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R. YeboahR. Yeboah</t>
+          <t>R. JanssonR. Jansson</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>108</v>
+        <v>302</v>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>500</v>
+        <v>536</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>V. SvenssonV. Svensson</t>
+          <t>M. LarssonM. Larsson</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>91</v>
+        <v>307</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>495</v>
+        <v>528</v>
       </c>
     </row>
     <row r="66">
@@ -2015,466 +2017,466 @@
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>128</v>
+        <v>223</v>
       </c>
       <c r="F66" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>492</v>
+        <v>525</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>F. NsabiyumvaF. Nsabiyumva</t>
+          <t>O. RosengrenO. Rosengren</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="F67" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>488</v>
+        <v>524</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>J. Une-LarssonJ. Une-Larsson</t>
+          <t>R. Wendin ThomassonR. Wendin Thomasson</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>474</v>
+        <v>516</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>J. AsoroJ. Asoro</t>
+          <t>C. RÃ¶slerC. RÃ¶sler</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>19</v>
+        <v>298</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
-        <v>474</v>
+        <v>513</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>C. StyffeC. Styffe</t>
+          <t>A. MannehA. Manneh</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>193</v>
+        <v>246</v>
       </c>
       <c r="F70" t="n">
         <v>9</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H70" t="n">
-        <v>466</v>
+        <v>512</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>J. GustavssonJ. Gustavsson</t>
+          <t>M. TenhoM. Tenho</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>194</v>
+        <v>307</v>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>464</v>
+        <v>498</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A. NorénA. Norén</t>
+          <t>M. HansenM. Hansen</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" t="n">
+        <v>294</v>
+      </c>
+      <c r="F72" t="n">
+        <v>14</v>
+      </c>
+      <c r="G72" t="n">
         <v>2</v>
       </c>
-      <c r="E72" t="n">
-        <v>194</v>
-      </c>
-      <c r="F72" t="n">
-        <v>9</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1</v>
-      </c>
       <c r="H72" t="n">
-        <v>464</v>
+        <v>490</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>R. KaibR. Kaib</t>
+          <t>O. KrusnellO. Krusnell</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>97</v>
+        <v>294</v>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H73" t="n">
-        <v>464</v>
+        <v>490</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>R. GojaniR. Gojani</t>
+          <t>F. HelanderF. Helander</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>39</v>
+        <v>302</v>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>462</v>
+        <v>477</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A. ErlingmarkA. Erlingmark</t>
+          <t>M. DyrestamM. Dyrestam</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="F75" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A. JallowA. Jallow</t>
+          <t>J. AllanssonJ. Allansson</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>T. HeintzT. Heintz</t>
+          <t>A. WÃ¤ngbergA. WÃ¤ngberg</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="F77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>D. SundgrenD. Sundgren</t>
+          <t>A. SkogmarA. Skogmar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="F78" t="n">
         <v>4</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>450</v>
+        <v>462</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A. Timossi AnderssonA. Timossi Andersson</t>
+          <t>R. MohammedR. Mohammed</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="F79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>446</v>
+        <v>460</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>S. GefvertS. Gefvert</t>
+          <t>K. KarlssonK. Karlsson</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F80" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>H. FinndellH. Finndell</t>
+          <t>F. WintherF. Winther</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
-        <v>429</v>
+        <v>445</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>K. KarlssonK. Karlsson</t>
+          <t>J. GustavssonJ. Gustavsson</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>68</v>
+        <v>289</v>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>397</v>
+        <v>436</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>V. LindV. Lind</t>
+          <t>A. BomanA. Boman</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>68</v>
+        <v>290</v>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H83" t="n">
-        <v>397</v>
+        <v>434</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>R. MohammedR. Mohammed</t>
+          <t>A. Timossi AnderssonA. Timossi Andersson</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>116</v>
+        <v>294</v>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>388</v>
+        <v>429</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C. PaveyC. Pavey</t>
+          <t>J. PerssonJ. Persson</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F85" t="n">
         <v>3</v>
@@ -2483,190 +2485,190 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>380</v>
+        <v>429</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>M. TenhoM. Tenho</t>
+          <t>N. Girmai NetabayN. Girmai Netabay</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>379</v>
+        <v>426</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>A. HellemaaA. Hellemaa</t>
+          <t>B. LaturnusB. Laturnus</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>24</v>
+        <v>276</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H87" t="n">
-        <v>375</v>
+        <v>424</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Z. YohannaZ. Yohanna</t>
+          <t>T. TekieT. Tekie</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="F88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>371</v>
+        <v>422</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>A. BomanA. Boman</t>
+          <t>A. LundkvistA. Lundkvist</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>97</v>
+        <v>302</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>371</v>
+        <v>417</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>O. RosengrenO. Rosengren</t>
+          <t>O. Victor OkekeO. Victor Okeke</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="F90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>367</v>
+        <v>403</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>M. DyrestamM. Dyrestam</t>
+          <t>D. KruseD. Kruse</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>197</v>
+        <v>294</v>
       </c>
       <c r="F91" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H91" t="n">
-        <v>365</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>S. OlssonS. Olsson</t>
+          <t>J. HoveJ. Hove</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>197</v>
+        <v>296</v>
       </c>
       <c r="F92" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>365</v>
+        <v>395</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A. DoumbiaA. Doumbia</t>
+          <t>T. MiettinenT. Miettinen</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F93" t="n">
         <v>6</v>
@@ -2675,46 +2677,46 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>364</v>
+        <v>391</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>T. LundberghT. Lundbergh</t>
+          <t>S. PapagiannopoulosS. Papagiannopoulos</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>360</v>
+        <v>391</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>L. SætraL. Sætra</t>
+          <t>O. AdinduO. Adindu</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
@@ -2723,55 +2725,55 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>360</v>
+        <v>391</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>J. MagnússonJ. Magnússon</t>
+          <t>S. GefvertS. Gefvert</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>301</v>
       </c>
       <c r="F96" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>341</v>
+        <v>389</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>A. MujanićA. Mujanić</t>
+          <t>H. FinndellH. Finndell</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E97" t="n">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G97" t="n">
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>338</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98">
@@ -2783,266 +2785,266 @@
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>333</v>
+        <v>384</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>M. BaggesenM. Baggesen</t>
+          <t>H. SkoglundH. Skoglund</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>164</v>
+        <v>283</v>
       </c>
       <c r="F99" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>329</v>
+        <v>382</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>S. HolménS. Holmén</t>
+          <t>O. CottonO. Cotton</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>329</v>
+        <v>375</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>M. ParkerM. Parker</t>
+          <t>A. HellemaaA. Hellemaa</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>197</v>
+        <v>24</v>
       </c>
       <c r="F101" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>320</v>
+        <v>375</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>S. HedlundS. Hedlund</t>
+          <t>C. PaveyC. Pavey</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" t="n">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="F102" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>318</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B. WembangomoB. Wembangomo</t>
+          <t>S. DiataraS. Diatara</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E103" t="n">
-        <v>201</v>
+        <v>296</v>
       </c>
       <c r="F103" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>313</v>
+        <v>365</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>T. PetterssonT. Pettersson</t>
+          <t>N. PerssonN. Persson</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="F104" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>303</v>
+        <v>363</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>V. GustafsonV. Gustafson</t>
+          <t>A. DoumbiaA. Doumbia</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
-        <v>125</v>
+        <v>274</v>
       </c>
       <c r="F105" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>288</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Villiam GranathVilliam Granath</t>
+          <t>F. NsabiyumvaF. Nsabiyumva</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E106" t="n">
-        <v>95</v>
+        <v>301</v>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>284</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>I. FofanaI. Fofana</t>
+          <t>Z. RÃ¥vikZ. RÃ¥vik</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>95</v>
+        <v>201</v>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>284</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>M. SiltanenM. Siltanen</t>
+          <t>B. WembangomoB. Wembangomo</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108" t="n">
-        <v>95</v>
+        <v>302</v>
       </c>
       <c r="F108" t="n">
+        <v>10</v>
+      </c>
+      <c r="G108" t="n">
         <v>2</v>
       </c>
-      <c r="G108" t="n">
-        <v>1</v>
-      </c>
       <c r="H108" t="n">
-        <v>284</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>H. SletsjøeH. Sletsjøe</t>
+          <t>H. HilveniusH. Hilvenius</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -3050,263 +3052,263 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>281</v>
+        <v>356</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>J. RingJ. Ring</t>
+          <t>B. CelinaB. Celina</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
-        <v>97</v>
+        <v>257</v>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" t="n">
-        <v>278</v>
+        <v>350</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>D. KruseD. Kruse</t>
+          <t>M. RaffertyM. Rafferty</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E111" t="n">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="F111" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G111" t="n">
         <v>2</v>
       </c>
       <c r="H111" t="n">
-        <v>276</v>
+        <v>341</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>D. PaulsonD. Paulson</t>
+          <t>I. FofanaI. Fofana</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>276</v>
+        <v>340</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>T. AliT. Ali</t>
+          <t>S. OlssonS. Olsson</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E113" t="n">
-        <v>98</v>
+        <v>298</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>276</v>
+        <v>332</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>O. Victor OkekeO. Victor Okeke</t>
+          <t>V. GustafsonV. Gustafson</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E114" t="n">
-        <v>33</v>
+        <v>191</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>273</v>
+        <v>330</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>S. AndersenS. Andersen</t>
+          <t>A. NilssonA. Nilsson</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>269</v>
+        <v>329</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>J. LindbergJ. Lindberg</t>
+          <t>P. JanssonP. Jansson</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E116" t="n">
-        <v>201</v>
+        <v>309</v>
       </c>
       <c r="F116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G116" t="n">
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>269</v>
+        <v>320</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>M. HansenM. Hansen</t>
+          <t>R. KaibR. Kaib</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E117" t="n">
-        <v>101</v>
+        <v>257</v>
       </c>
       <c r="F117" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>267</v>
+        <v>315</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>T. SanaT. Sana</t>
+          <t>M. ParkerM. Parker</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E118" t="n">
-        <v>170</v>
+        <v>289</v>
       </c>
       <c r="F118" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>265</v>
+        <v>311</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>O. BergO. Berg</t>
+          <t>L. TidstrandL. Tidstrand</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>265</v>
+        <v>310</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>A. LayouniA. Layouni</t>
+          <t>O. Steinke BrÃ¥nbyO. Steinke BrÃ¥nby</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -3314,47 +3316,47 @@
         <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>173</v>
+        <v>29</v>
       </c>
       <c r="F120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>J. BeckJ. Beck</t>
+          <t>M. LindbergM. Lindberg</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E121" t="n">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="F121" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>255</v>
+        <v>306</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>W. SvenssonW. Svensson</t>
+          <t>T. PetterssonT. Pettersson</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -3362,47 +3364,47 @@
         <v>2</v>
       </c>
       <c r="E122" t="n">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>250</v>
+        <v>303</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>H. CarneilH. Carneil</t>
+          <t>S. AndersenS. Andersen</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>75</v>
+        <v>302</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>240</v>
+        <v>298</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>W. MilovanovićW. Milovanović</t>
+          <t>A. ÄardaklijaA. Äardaklija</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3410,7 +3412,7 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F124" t="n">
         <v>2</v>
@@ -3419,214 +3421,214 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>237</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>O. OkekeO. Okeke</t>
+          <t>M. HeierM. Heier</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125" t="n">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="F125" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>222</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>O. LiimattaO. Liimatta</t>
+          <t>R. GojaniR. Gojani</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E126" t="n">
-        <v>41</v>
+        <v>217</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>220</v>
+        <v>290</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>M. HeierM. Heier</t>
+          <t>S. HedlundS. Hedlund</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E127" t="n">
-        <v>91</v>
+        <v>249</v>
       </c>
       <c r="F127" t="n">
+        <v>6</v>
+      </c>
+      <c r="G127" t="n">
         <v>2</v>
       </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
       <c r="H127" t="n">
-        <v>198</v>
+        <v>289</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>N. BesaraN. Besara</t>
+          <t>A. LayouniA. Layouni</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E128" t="n">
-        <v>92</v>
+        <v>266</v>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>196</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>T. StavitskiT. Stavitski</t>
+          <t>Villiam GranathVilliam Granath</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E129" t="n">
-        <v>47</v>
+        <v>173</v>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>191</v>
+        <v>260</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>P. JohanssonP. Johansson</t>
+          <t>V. SvenssonV. Svensson</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E130" t="n">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="F130" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>189</v>
+        <v>257</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>R. PetrovicR. Petrovic</t>
+          <t>J. LindbergJ. Lindberg</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E131" t="n">
-        <v>95</v>
+        <v>283</v>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>189</v>
+        <v>254</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>J. HoveJ. Hove</t>
+          <t>J. MagnÃºssonJ. MagnÃºsson</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E132" t="n">
-        <v>97</v>
+        <v>286</v>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>186</v>
+        <v>252</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>M. DiagneM. Diagne</t>
+          <t>M. HallbergM. Hallberg</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E133" t="n">
-        <v>203</v>
+        <v>144</v>
       </c>
       <c r="F133" t="n">
         <v>3</v>
@@ -3635,14 +3637,14 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>W. HofvanderW. Hofvander</t>
+          <t>W. SvenssonW. Svensson</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3650,7 +3652,7 @@
         <v>2</v>
       </c>
       <c r="E134" t="n">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="F134" t="n">
         <v>3</v>
@@ -3659,110 +3661,110 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>176</v>
+        <v>250</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>J. Hernández MesasJ. Hernández Mesas</t>
+          <t>O. LiimattaO. Liimatta</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E135" t="n">
-        <v>51</v>
+        <v>218</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>176</v>
+        <v>248</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>T. SilverholtT. Silverholt</t>
+          <t>D. BeÅ¡iroviÄD. BeÅ¡iroviÄ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E136" t="n">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>171</v>
+        <v>243</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>A. AndreassonA. Andreasson</t>
+          <t>T. LundberghT. Lundbergh</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>147</v>
+        <v>238</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Y. KarabelyovY. Karabelyov</t>
+          <t>M. SiltanenM. Siltanen</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E138" t="n">
-        <v>65</v>
+        <v>307</v>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>138</v>
+        <v>235</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>A. LundkvistA. Lundkvist</t>
+          <t>A. MujaniÄA. MujaniÄ</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3770,95 +3772,95 @@
         <v>2</v>
       </c>
       <c r="E139" t="n">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="F139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>134</v>
+        <v>227</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>D. VukojevićD. Vukojević</t>
+          <t>J. Une-LarssonJ. Une-Larsson</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E140" t="n">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>132</v>
+        <v>225</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>K. AckermannK. Ackermann</t>
+          <t>T. SanaT. Sana</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E141" t="n">
-        <v>68</v>
+        <v>243</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>132</v>
+        <v>222</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>K. ThórdarsonK. Thórdarson</t>
+          <t>M. BaggesenM. Baggesen</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E142" t="n">
-        <v>69</v>
+        <v>244</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>130</v>
+        <v>221</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>A. ZeneliA. Zeneli</t>
+          <t>J. RingJ. Ring</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3866,151 +3868,151 @@
         <v>2</v>
       </c>
       <c r="E143" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>119</v>
+        <v>213</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>N. ChourakN. Chourak</t>
+          <t>I. CissÃ©I. CissÃ©</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E144" t="n">
-        <v>76</v>
+        <v>296</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H144" t="n">
-        <v>118</v>
+        <v>213</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>P. ÅslundP. Åslund</t>
+          <t>M. DiagneM. Diagne</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E145" t="n">
-        <v>76</v>
+        <v>301</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H145" t="n">
-        <v>118</v>
+        <v>209</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>O. JohanssonO. Johansson</t>
+          <t>W. MilovanoviÄW. MilovanoviÄ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E146" t="n">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>113</v>
+        <v>203</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>M. Klarlund NielsenM. Klarlund Nielsen</t>
+          <t>A. AndreassonA. Andreasson</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E147" t="n">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>111</v>
+        <v>196</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>P. FrickP. Frick</t>
+          <t>B. HeglandB. Hegland</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
+        <v>3</v>
+      </c>
+      <c r="E148" t="n">
+        <v>280</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4</v>
+      </c>
+      <c r="G148" t="n">
         <v>2</v>
       </c>
-      <c r="E148" t="n">
-        <v>85</v>
-      </c>
-      <c r="F148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0</v>
-      </c>
       <c r="H148" t="n">
-        <v>106</v>
+        <v>193</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Á. SamuelsenÁ. Samuelsen</t>
+          <t>J. KarlssonJ. Karlsson</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E149" t="n">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="F149" t="n">
         <v>1</v>
@@ -4019,14 +4021,14 @@
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>102</v>
+        <v>191</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>P. AbrahamP. Abraham</t>
+          <t>T. StavitskiT. Stavitski</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -4034,7 +4036,7 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="F150" t="n">
         <v>1</v>
@@ -4043,262 +4045,262 @@
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>98</v>
+        <v>191</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>D. BeširovićD. Beširović</t>
+          <t>M. KarlssonM. Karlsson</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E151" t="n">
-        <v>97</v>
+        <v>283</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" t="n">
-        <v>93</v>
+        <v>191</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>I. CisséI. Cissé</t>
+          <t>S. AlioumS. Alioum</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E152" t="n">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" t="n">
-        <v>93</v>
+        <v>191</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>J. AllanssonJ. Allansson</t>
+          <t>Z. YohannaZ. Yohanna</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E153" t="n">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>93</v>
+        <v>189</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>O. KapsimalisO. Kapsimalis</t>
+          <t>D. PaulsonD. Paulson</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>93</v>
+        <v>189</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>P. JanssonP. Jansson</t>
+          <t>V. LindV. Lind</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E155" t="n">
-        <v>98</v>
+        <v>238</v>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>92</v>
+        <v>189</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>I. BjerkeboI. Bjerkebo</t>
+          <t>Mohamed SoumahMohamed Soumah</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" t="n">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>90</v>
+        <v>186</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>L. FritzsonL. Fritzson</t>
+          <t>N. ChourakN. Chourak</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E157" t="n">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>90</v>
+        <v>185</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>M. LindbergM. Lindberg</t>
+          <t>W. HofvanderW. Hofvander</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E158" t="n">
-        <v>100</v>
+        <v>245</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>90</v>
+        <v>184</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>O. ThoresonO. Thoreson</t>
+          <t>S. HakÅ¡abanoviÄS. HakÅ¡abanoviÄ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E159" t="n">
-        <v>100</v>
+        <v>196</v>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H159" t="n">
-        <v>90</v>
+        <v>184</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>R. UreR. Ure</t>
+          <t>K. AckermannK. Ackermann</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160" t="n">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>90</v>
+        <v>182</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>A. TaonsaA. Taonsa</t>
+          <t>L. BergquistL. Bergquist</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E161" t="n">
-        <v>203</v>
+        <v>99</v>
       </c>
       <c r="F161" t="n">
         <v>2</v>
@@ -4307,14 +4309,14 @@
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>89</v>
+        <v>182</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>V. LarssonV. Larsson</t>
+          <t>J. HernÃ¡ndez MesasJ. HernÃ¡ndez Mesas</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -4322,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
@@ -4331,182 +4333,182 @@
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>88</v>
+        <v>176</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>G. LindgrenG. Lindgren</t>
+          <t>T. AliT. Ali</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="n">
+        <v>3</v>
+      </c>
+      <c r="E163" t="n">
+        <v>309</v>
+      </c>
+      <c r="F163" t="n">
+        <v>4</v>
+      </c>
+      <c r="G163" t="n">
         <v>2</v>
       </c>
-      <c r="E163" t="n">
-        <v>104</v>
-      </c>
-      <c r="F163" t="n">
-        <v>1</v>
-      </c>
-      <c r="G163" t="n">
-        <v>0</v>
-      </c>
       <c r="H163" t="n">
-        <v>87</v>
+        <v>175</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>S. AlioumS. Alioum</t>
+          <t>S. StrandS. Strand</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E164" t="n">
-        <v>138</v>
+        <v>213</v>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>65</v>
+        <v>169</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>N. HultN. Hult</t>
+          <t>D. VukojeviÄD. VukojeviÄ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E165" t="n">
+        <v>218</v>
+      </c>
+      <c r="F165" t="n">
+        <v>3</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="n">
         <v>165</v>
-      </c>
-      <c r="F165" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" t="n">
-        <v>1</v>
-      </c>
-      <c r="H165" t="n">
-        <v>55</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>A. SvanbäckA. Svanbäck</t>
+          <t>T. SilverholtT. Silverholt</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E166" t="n">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>53</v>
+        <v>161</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>A. WibergA. Wiberg</t>
+          <t>J. BeckJ. Beck</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="n">
+        <v>3</v>
+      </c>
+      <c r="E167" t="n">
+        <v>170</v>
+      </c>
+      <c r="F167" t="n">
         <v>2</v>
       </c>
-      <c r="E167" t="n">
-        <v>185</v>
-      </c>
-      <c r="F167" t="n">
-        <v>0</v>
-      </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>J. BergströmJ. Bergström</t>
+          <t>Sebastian OhlssonSebastian Ohlsson</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E168" t="n">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>M. LadefogedM. Ladefoged</t>
+          <t>S. OppongS. Oppong</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="n">
+        <v>3</v>
+      </c>
+      <c r="E169" t="n">
+        <v>125</v>
+      </c>
+      <c r="F169" t="n">
         <v>2</v>
       </c>
-      <c r="E169" t="n">
-        <v>164</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0</v>
-      </c>
       <c r="G169" t="n">
         <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>A. BoudahA. Boudah</t>
+          <t>O. OkekeO. Okeke</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -4514,47 +4516,47 @@
         <v>2</v>
       </c>
       <c r="E170" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>N. ChristofferssonN. Christoffersson</t>
+          <t>Y. KarabelyovY. Karabelyov</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>J. TibblingJ. Tibbling</t>
+          <t>P. JohanssonP. Johansson</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -4562,119 +4564,119 @@
         <v>2</v>
       </c>
       <c r="E172" t="n">
-        <v>91</v>
+        <v>208</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>K. GunnarssonK. Gunnarsson</t>
+          <t>I. BjerkeboI. Bjerkebo</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E173" t="n">
-        <v>90</v>
+        <v>279</v>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>S. NgaboS. Ngabo</t>
+          <t>V. ErikssonV. Eriksson</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E174" t="n">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>R. LeanderssonR. Leandersson</t>
+          <t>R. UreR. Ure</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E175" t="n">
-        <v>70</v>
+        <v>284</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>M. FengerM. Fenger</t>
+          <t>O. JohanssonO. Johansson</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="n">
+        <v>3</v>
+      </c>
+      <c r="E176" t="n">
+        <v>217</v>
+      </c>
+      <c r="F176" t="n">
         <v>2</v>
       </c>
-      <c r="E176" t="n">
-        <v>58</v>
-      </c>
-      <c r="F176" t="n">
-        <v>0</v>
-      </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H176" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>L. ÖstmanL. Östman</t>
+          <t>O. BergO. Berg</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -4682,311 +4684,311 @@
         <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>A. SigurpálssonA. Sigurpálsson</t>
+          <t>L. ArvidssonL. Arvidsson</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>D. HodzicD. Hodzic</t>
+          <t>Montader MadjedMontader Madjed</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E179" t="n">
-        <v>34</v>
+        <v>235</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B. Bang-KittilsenB. Bang-Kittilsen</t>
+          <t>H. CarneilH. Carneil</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
+        <v>3</v>
+      </c>
+      <c r="E180" t="n">
+        <v>161</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="n">
         <v>2</v>
       </c>
-      <c r="E180" t="n">
-        <v>33</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" t="n">
-        <v>0</v>
-      </c>
       <c r="H180" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>J. KarlssonJ. Karlsson</t>
+          <t>P. FrickP. Frick</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
+        <v>3</v>
+      </c>
+      <c r="E181" t="n">
+        <v>164</v>
+      </c>
+      <c r="F181" t="n">
         <v>2</v>
       </c>
-      <c r="E181" t="n">
-        <v>28</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0</v>
-      </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>S. LagerlundS. Lagerlund</t>
+          <t>N. BesaraN. Besara</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E182" t="n">
-        <v>7</v>
+        <v>247</v>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>C. RosenqvistC. Rosenqvist</t>
+          <t>J. AsoroJ. Asoro</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E183" t="n">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="F183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>C. Sagoe JrC. Sagoe Jr</t>
+          <t>Ã. SamuelsenÃ. Samuelsen</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184" t="n">
+        <v>88</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
         <v>102</v>
-      </c>
-      <c r="F184" t="n">
-        <v>0</v>
-      </c>
-      <c r="G184" t="n">
-        <v>0</v>
-      </c>
-      <c r="H184" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>V. TyrénV. Tyrén</t>
+          <t>M. IllaryM. Illary</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>S. DiataraS. Diatara</t>
+          <t>R. PetrovicR. Petrovic</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E186" t="n">
+        <v>271</v>
+      </c>
+      <c r="F186" t="n">
+        <v>3</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
         <v>100</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0</v>
-      </c>
-      <c r="G186" t="n">
-        <v>0</v>
-      </c>
-      <c r="H186" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>E. BotheimE. Botheim</t>
+          <t>C. Sagoe JrC. Sagoe Jr</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E187" t="n">
-        <v>98</v>
+        <v>280</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H187" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>L. BjörklundL. Björklund</t>
+          <t>A. ZeneliA. Zeneli</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E188" t="n">
+        <v>187</v>
+      </c>
+      <c r="F188" t="n">
+        <v>2</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
         <v>96</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0</v>
-      </c>
-      <c r="G188" t="n">
-        <v>0</v>
-      </c>
-      <c r="H188" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>M. KarlssonM. Karlsson</t>
+          <t>E. BarsoumE. Barsoum</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E189" t="n">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>V. ErikssonV. Eriksson</t>
+          <t>O. KapsimalisO. Kapsimalis</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4994,47 +4996,47 @@
         <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Neo JönssonNeo Jönsson</t>
+          <t>M. Klarlund NielsenM. Klarlund Nielsen</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E191" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>K. LienK. Lien</t>
+          <t>M. MarquÃ©sM. MarquÃ©s</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -5042,559 +5044,561 @@
         <v>1</v>
       </c>
       <c r="E192" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>M. PerssonM. Persson</t>
+          <t>K. GunnarssonK. Gunnarsson</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E193" t="n">
+        <v>109</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
         <v>83</v>
-      </c>
-      <c r="F193" t="n">
-        <v>0</v>
-      </c>
-      <c r="G193" t="n">
-        <v>0</v>
-      </c>
-      <c r="H193" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Montader MadjedMontader Madjed</t>
+          <t>A. KouameA. Kouame</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E194" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="F194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>B. HeglandB. Hegland</t>
+          <t>P. Ã+slundP. Ã+slund</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E195" t="n">
-        <v>76</v>
+        <v>225</v>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>S. SalterS. Salter</t>
+          <t>K. ThÃ³rdarsonK. ThÃ³rdarson</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E196" t="n">
-        <v>76</v>
+        <v>234</v>
       </c>
       <c r="F196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>A. ChristiansenA. Christiansen</t>
+          <t>A. WibergA. Wiberg</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E197" t="n">
-        <v>75</v>
+        <v>235</v>
       </c>
       <c r="F197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H197" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>T. AyariT. Ayari</t>
+          <t>L. HienL. Hien</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E198" t="n">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>O. FalleniusO. Fallenius</t>
+          <t>G. LindgrenG. Lindgren</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E199" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="F199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>A. SigurdssonA. Sigurdsson</t>
+          <t>H. SletsjÃ¸eH. SletsjÃ¸e</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E200" t="n">
-        <v>65</v>
+        <v>124</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>M. HallbergM. Hallberg</t>
+          <t>V. LarssonV. Larsson</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E201" t="n">
-        <v>63</v>
+        <v>270</v>
       </c>
       <c r="F201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>M. SöderbäckM. Söderbäck</t>
+          <t>R. ThorkelssonR. Thorkelsson</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E202" t="n">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>M. IllaryM. Illary</t>
+          <t>A. TaonsaA. Taonsa</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E203" t="n">
-        <v>57</v>
+        <v>283</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>M. AnderssonM. Andersson</t>
+          <t>L. FritzsonL. Fritzson</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E204" t="n">
-        <v>56</v>
+        <v>296</v>
       </c>
       <c r="F204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>O. PetterssonO. Pettersson</t>
+          <t>C. RosenqvistC. Rosenqvist</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E205" t="n">
-        <v>40</v>
+        <v>302</v>
       </c>
       <c r="F205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Emeka NnamaniEmeka Nnamani</t>
+          <t>D. IssoD. Isso</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E206" t="n">
-        <v>39</v>
+        <v>151</v>
       </c>
       <c r="F206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>S. NgoualiS. Ngouali</t>
+          <t>O. FalleniusO. Fallenius</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E207" t="n">
-        <v>38</v>
+        <v>172</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>D. IssoD. Isso</t>
+          <t>P. AbrahamP. Abraham</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E208" t="n">
-        <v>33</v>
+        <v>182</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>O. SjöstrandO. Sjöstrand</t>
+          <t>O. SjÃ¶strandO. SjÃ¶strand</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E209" t="n">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="F209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>E. BarsoumE. Barsoum</t>
+          <t>M. SÃ¶derbÃ¤ckM. SÃ¶derbÃ¤ck</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E210" t="n">
-        <v>32</v>
+        <v>196</v>
       </c>
       <c r="F210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>O. LeonardssonO. Leonardsson</t>
+          <t>N. HultN. Hult</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E211" t="n">
-        <v>32</v>
+        <v>231</v>
       </c>
       <c r="F211" t="n">
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H211" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Sebastian OhlssonSebastian Ohlsson</t>
+          <t>V. TyrÃ©nV. TyrÃ©n</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E212" t="n">
-        <v>32</v>
+        <v>249</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>J. AgbonifoJ. Agbonifo</t>
+          <t>A. SvanbÃ¤ckA. SvanbÃ¤ck</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E213" t="n">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="F213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>N. PerssonN. Persson</t>
+          <t>E. BotheimE. Botheim</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E214" t="n">
-        <v>28</v>
+        <v>276</v>
       </c>
       <c r="F214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>B. BrantlindB. Brantlind</t>
+          <t>K. LienK. Lien</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E215" t="n">
-        <v>27</v>
+        <v>296</v>
       </c>
       <c r="F215" t="n">
         <v>0</v>
@@ -5610,15 +5614,15 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>I. JagneI. Jagne</t>
+          <t>J. BergstrÃ¶mJ. BergstrÃ¶m</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E216" t="n">
-        <v>27</v>
+        <v>275</v>
       </c>
       <c r="F216" t="n">
         <v>0</v>
@@ -5634,15 +5638,15 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>J. OkkelsJ. Okkels</t>
+          <t>L. BjÃ¶rklundL. BjÃ¶rklund</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E217" t="n">
-        <v>26</v>
+        <v>274</v>
       </c>
       <c r="F217" t="n">
         <v>0</v>
@@ -5658,15 +5662,15 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>K. FillingK. Filling</t>
+          <t>M. LadefogedM. Ladefoged</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E218" t="n">
-        <v>26</v>
+        <v>244</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
@@ -5682,15 +5686,15 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>L. BergquistL. Bergquist</t>
+          <t>A. BoudahA. Boudah</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E219" t="n">
-        <v>26</v>
+        <v>224</v>
       </c>
       <c r="F219" t="n">
         <v>0</v>
@@ -5706,15 +5710,15 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>E. YeboahE. Yeboah</t>
+          <t>S. SalterS. Salter</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E220" t="n">
-        <v>23</v>
+        <v>220</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
@@ -5730,15 +5734,15 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>G. RappG. Rapp</t>
+          <t>Neo JÃ¶nssonNeo JÃ¶nsson</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E221" t="n">
-        <v>23</v>
+        <v>218</v>
       </c>
       <c r="F221" t="n">
         <v>0</v>
@@ -5754,15 +5758,15 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>S. OppongS. Oppong</t>
+          <t>M. PerssonM. Persson</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E222" t="n">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
@@ -5778,15 +5782,15 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>S. StrandS. Strand</t>
+          <t>J. TibblingJ. Tibbling</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E223" t="n">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="F223" t="n">
         <v>0</v>
@@ -5802,15 +5806,15 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>A. SaeedA. Saeed</t>
+          <t>O. PetterssonO. Pettersson</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E224" t="n">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="F224" t="n">
         <v>0</v>
@@ -5826,15 +5830,15 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>R. Wendin ThomassonR. Wendin Thomasson</t>
+          <t>N. ChristofferssonN. Christoffersson</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E225" t="n">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F225" t="n">
         <v>0</v>
@@ -5850,15 +5854,15 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>S. EkongS. Ekong</t>
+          <t>J. OkkelsJ. Okkels</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E226" t="n">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="F226" t="n">
         <v>0</v>
@@ -5874,15 +5878,15 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>V. AnderssonV. Andersson</t>
+          <t>O. FarajO. Faraj</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E227" t="n">
-        <v>17</v>
+        <v>121</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -5898,15 +5902,15 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>O. Steinke BrånbyO. Steinke Brånby</t>
+          <t>A. SigurdssonA. Sigurdsson</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E228" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="F228" t="n">
         <v>0</v>
@@ -5922,15 +5926,15 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>O. FarajO. Faraj</t>
+          <t>K. FillingK. Filling</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E229" t="n">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="F229" t="n">
         <v>0</v>
@@ -5946,15 +5950,15 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>L. HienL. Hien</t>
+          <t>M. FengerM. Fenger</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E230" t="n">
-        <v>12</v>
+        <v>106</v>
       </c>
       <c r="F230" t="n">
         <v>0</v>
@@ -5970,15 +5974,15 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>L. TidstrandL. Tidstrand</t>
+          <t>M. NarteyM. Nartey</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E231" t="n">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="F231" t="n">
         <v>0</v>
@@ -5994,15 +5998,15 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>P. LanghoffP. Langhoff</t>
+          <t>R. LeanderssonR. Leandersson</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E232" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
@@ -6018,15 +6022,15 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>S. ClemmensenS. Clemmensen</t>
+          <t>S. NgaboS. Ngabo</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E233" t="n">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="F233" t="n">
         <v>0</v>
@@ -6042,15 +6046,15 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>A. BerissonA. Berisson</t>
+          <t>Emeka NnamaniEmeka Nnamani</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E234" t="n">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="F234" t="n">
         <v>0</v>
@@ -6066,15 +6070,15 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>M. NarteyM. Nartey</t>
+          <t>B. Bang-KittilsenB. Bang-Kittilsen</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E235" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
@@ -6090,15 +6094,15 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>M. KaboréM. Kaboré</t>
+          <t>A. SigurpÃ¡lssonA. SigurpÃ¡lsson</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E236" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
@@ -6114,15 +6118,15 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>S. KoneS. Kone</t>
+          <t>S. EkongS. Ekong</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E237" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="F237" t="n">
         <v>0</v>
@@ -6138,15 +6142,15 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>W. KenndalW. Kenndal</t>
+          <t>D. HodzicD. Hodzic</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E238" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="F238" t="n">
         <v>0</v>
@@ -6162,15 +6166,15 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>M. HellisdalM. Hellisdal</t>
+          <t>L. ÃstmanL. Ãstman</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E239" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
@@ -6186,15 +6190,15 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>S. PapagiannopoulosS. Papagiannopoulos</t>
+          <t>O. LeonardssonO. Leonardsson</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E240" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="F240" t="n">
         <v>0</v>
@@ -6210,15 +6214,15 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>A. AbukarA. Abukar</t>
+          <t>P. LanghoffP. Langhoff</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E241" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F241" t="n">
         <v>0</v>
@@ -6234,15 +6238,15 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>A. AliA. Ali</t>
+          <t>T. AyariT. Ayari</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E242" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="F242" t="n">
         <v>0</v>
@@ -6258,15 +6262,15 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>A. AmoleA. Amole</t>
+          <t>J. AgbonifoJ. Agbonifo</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E243" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F243" t="n">
         <v>0</v>
@@ -6282,15 +6286,15 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>A. ČardaklijaA. Čardaklija</t>
+          <t>M. KaborÃ©M. KaborÃ©</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E244" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F244" t="n">
         <v>0</v>
@@ -6306,15 +6310,15 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>A. DjuricA. Djuric</t>
+          <t>M. AnderssonM. Andersson</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E245" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F245" t="n">
         <v>0</v>
@@ -6330,15 +6334,15 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>A. FaqaA. Faqa</t>
+          <t>B. BrantlindB. Brantlind</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E246" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F246" t="n">
         <v>0</v>
@@ -6354,15 +6358,15 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>A. GhitaA. Ghita</t>
+          <t>E. YeboahE. Yeboah</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E247" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F247" t="n">
         <v>0</v>
@@ -6378,15 +6382,15 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>A. HelmA. Helm</t>
+          <t>O. HagenO. Hagen</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E248" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F248" t="n">
         <v>0</v>
@@ -6402,15 +6406,15 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>A. HöögA. Höög</t>
+          <t>V. AnderssonV. Andersson</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E249" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F249" t="n">
         <v>0</v>
@@ -6426,15 +6430,15 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>A. KeitaA. Keita</t>
+          <t>K. SeverK. Sever</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E250" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F250" t="n">
         <v>0</v>
@@ -6450,15 +6454,15 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>A. KurochkinA. Kurochkin</t>
+          <t>S. LagerlundS. Lagerlund</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E251" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F251" t="n">
         <v>0</v>
@@ -6474,15 +6478,15 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>A. LindgrenA. Lindgren</t>
+          <t>A. ChristiansenA. Christiansen</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E252" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F252" t="n">
         <v>0</v>
@@ -6498,15 +6502,15 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
-          <t>A. MagashyA. Magashy</t>
+          <t>A. AliA. Ali</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E253" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F253" t="n">
         <v>0</v>
@@ -6522,15 +6526,15 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
-          <t>A. MucolliA. Mucolli</t>
+          <t>M. BawaM. Bawa</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E254" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F254" t="n">
         <v>0</v>
@@ -6546,15 +6550,15 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
-          <t>A. NilssonA. Nilsson</t>
+          <t>E. FlatakerE. Flataker</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E255" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
@@ -6570,15 +6574,15 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
-          <t>A. OlusanyaA. Olusanya</t>
+          <t>S. NgoualiS. Ngouali</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E256" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F256" t="n">
         <v>0</v>
@@ -6594,15 +6598,15 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
-          <t>A. PalacA. Palac</t>
+          <t>D. GudjohnsenD. Gudjohnsen</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F257" t="n">
         <v>0</v>
@@ -6618,15 +6622,15 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>A. RedkinA. Redkin</t>
+          <t>N. VasiÄN. VasiÄ</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E258" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F258" t="n">
         <v>0</v>
@@ -6642,15 +6646,15 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>A. SabriyeA. Sabriye</t>
+          <t>I. JagneI. Jagne</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F259" t="n">
         <v>0</v>
@@ -6666,15 +6670,15 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>A. SkogmarA. Skogmar</t>
+          <t>A. TaranisA. Taranis</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
@@ -6690,15 +6694,15 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>A. StåhlA. Ståhl</t>
+          <t>G. RappG. Rapp</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E261" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F261" t="n">
         <v>0</v>
@@ -6714,15 +6718,15 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>A. TaranisA. Taranis</t>
+          <t>C. GustafssonC. Gustafsson</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F262" t="n">
         <v>0</v>
@@ -6738,15 +6742,15 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>A. TashevciA. Tashevci</t>
+          <t>A. SaeedA. Saeed</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E263" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F263" t="n">
         <v>0</v>
@@ -6762,15 +6766,15 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>A. WahlundA. Wahlund</t>
+          <t>J. AzulayJ. Azulay</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F264" t="n">
         <v>0</v>
@@ -6786,15 +6790,15 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>B. Asuman DankwahB. Asuman Dankwah</t>
+          <t>J. LjungqvistJ. Ljungqvist</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E265" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F265" t="n">
         <v>0</v>
@@ -6810,15 +6814,15 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>B. EngdahlB. Engdahl</t>
+          <t>M. EbietomereM. Ebietomere</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E266" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F266" t="n">
         <v>0</v>
@@ -6834,15 +6838,15 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>B. HedlöfB. Hedlöf</t>
+          <t>A. FaqaA. Faqa</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E267" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F267" t="n">
         <v>0</v>
@@ -6858,15 +6862,15 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>B. HusseinB. Hussein</t>
+          <t>B. KurtulusB. Kurtulus</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E268" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F268" t="n">
         <v>0</v>
@@ -6882,15 +6886,15 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>B. KurtulusB. Kurtulus</t>
+          <t>O. LindbergO. Lindberg</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E269" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F269" t="n">
         <v>0</v>
@@ -6906,15 +6910,15 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>B. MagnussonB. Magnusson</t>
+          <t>B. Asuman DankwahB. Asuman Dankwah</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F270" t="n">
         <v>0</v>
@@ -6930,15 +6934,15 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>B. MilovanovB. Milovanov</t>
+          <t>V. JohanssonV. Johansson</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E271" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F271" t="n">
         <v>0</v>
@@ -6954,15 +6958,15 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>BusanelloBusanello</t>
+          <t>A. KurochkinA. Kurochkin</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E272" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F272" t="n">
         <v>0</v>
@@ -6978,15 +6982,15 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>C. GustafssonC. Gustafsson</t>
+          <t>A. OlusanyaA. Olusanya</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F273" t="n">
         <v>0</v>
@@ -7002,15 +7006,15 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>C. OtokweforC. Otokwefor</t>
+          <t>A. DjuricA. Djuric</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E274" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F274" t="n">
         <v>0</v>
@@ -7026,15 +7030,15 @@
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>C. TchouanteC. Tchouante</t>
+          <t>S. ClemmensenS. Clemmensen</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E275" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F275" t="n">
         <v>0</v>
@@ -7050,15 +7054,15 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>C. VindehallC. Vindehall</t>
+          <t>A. BerissonA. Berisson</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E276" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F276" t="n">
         <v>0</v>
@@ -7074,15 +7078,15 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>C. WawaC. Wawa</t>
+          <t>F. BeckmanF. Beckman</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F277" t="n">
         <v>0</v>
@@ -7098,15 +7102,15 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>D. BengtssonD. Bengtsson</t>
+          <t>S. KoneS. Kone</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F278" t="n">
         <v>0</v>
@@ -7122,15 +7126,15 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>D. CollanderD. Collander</t>
+          <t>W. KenndalW. Kenndal</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E279" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F279" t="n">
         <v>0</v>
@@ -7146,15 +7150,15 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>D. GudjohnsenD. Gudjohnsen</t>
+          <t>M. HellisdalM. Hellisdal</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F280" t="n">
         <v>0</v>
@@ -7170,7 +7174,7 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>D. KoffiD. Koffi</t>
+          <t>A. AbukarA. Abukar</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -7194,7 +7198,7 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>D. KrasniqiD. Krasniqi</t>
+          <t>A. AmoleA. Amole</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -7218,7 +7222,7 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>D. KrivosicD. Krivosic</t>
+          <t>A. GhitaA. Ghita</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -7242,7 +7246,7 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>D. StenssonD. Stensson</t>
+          <t>A. HelmA. Helm</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -7266,7 +7270,7 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Danilo Al SaedDanilo Al Saed</t>
+          <t>A. HÃ¶Ã¶gA. HÃ¶Ã¶g</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -7290,7 +7294,7 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>E. BotchwayE. Botchway</t>
+          <t>A. KeitaA. Keita</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -7314,7 +7318,7 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>E. EdhE. Edh</t>
+          <t>A. LindgrenA. Lindgren</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -7338,7 +7342,7 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>E. EkongE. Ekong</t>
+          <t>A. MagashyA. Magashy</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -7362,7 +7366,7 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>E. El-KhatemiE. El-Khatemi</t>
+          <t>A. MucolliA. Mucolli</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -7386,7 +7390,7 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>E. FlatakerE. Flataker</t>
+          <t>A. PalacA. Palac</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -7410,7 +7414,7 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>E. HedstromE. Hedstrom</t>
+          <t>A. RedkinA. Redkin</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -7434,7 +7438,7 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>E. LindellE. Lindell</t>
+          <t>A. SabriyeA. Sabriye</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -7458,7 +7462,7 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>E. Lwampindy BofuaE. Lwampindy Bofua</t>
+          <t>A. StÃ¥hlA. StÃ¥hl</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -7482,7 +7486,7 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>E. YonanE. Yonan</t>
+          <t>A. TashevciA. Tashevci</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -7506,7 +7510,7 @@
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>F. AronssonF. Aronsson</t>
+          <t>A. WahlundA. Wahlund</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -7530,7 +7534,7 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>F. BeckmanF. Beckman</t>
+          <t>B. EngdahlB. Engdahl</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -7554,7 +7558,7 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>F. Giuseppe NeatF. Giuseppe Neat</t>
+          <t>B. HedlÃ¶fB. HedlÃ¶f</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -7578,7 +7582,7 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>F. IhlerF. Ihler</t>
+          <t>B. MagnussonB. Magnusson</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -7602,7 +7606,7 @@
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>F. NissenF. Nissen</t>
+          <t>B. MilovanovB. Milovanov</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -7626,7 +7630,7 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>F. ÖhmanF. Öhman</t>
+          <t>C. OtokweforC. Otokwefor</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -7650,7 +7654,7 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>F. SchybergF. Schyberg</t>
+          <t>C. SelfvenC. Selfven</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -7674,7 +7678,7 @@
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>G. ErsoyG. Ersoy</t>
+          <t>C. TchouanteC. Tchouante</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -7698,7 +7702,7 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>G. FribergG. Friberg</t>
+          <t>C. VindehallC. Vindehall</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -7722,7 +7726,7 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>G. LajqiG. Lajqi</t>
+          <t>C. WawaC. Wawa</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -7746,7 +7750,7 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>G. LundgrenG. Lundgren</t>
+          <t>D. BengtssonD. Bengtsson</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -7770,7 +7774,7 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>H. ÅbergH. Åberg</t>
+          <t>D. CollanderD. Collander</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -7794,7 +7798,7 @@
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>H. Andersson MellaH. Andersson Mella</t>
+          <t>D. KoffiD. Koffi</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -7818,7 +7822,7 @@
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>H. AtolaH. Atola</t>
+          <t>D. KrasniqiD. Krasniqi</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -7842,7 +7846,7 @@
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>H. DahlqvistH. Dahlqvist</t>
+          <t>D. KrivosicD. Krivosic</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -7866,7 +7870,7 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>H. HilveniusH. Hilvenius</t>
+          <t>Danilo Al SaedDanilo Al Saed</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -7890,7 +7894,7 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>H. KarlssonH. Karlsson</t>
+          <t>E. BotchwayE. Botchway</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -7914,7 +7918,7 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>I. AdewaleI. Adewale</t>
+          <t>E. EdhE. Edh</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
@@ -7938,7 +7942,7 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>I. AtangaI. Atanga</t>
+          <t>E. EkongE. Ekong</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -7962,7 +7966,7 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>I. BuhariI. Buhari</t>
+          <t>E. El-KhatemiE. El-Khatemi</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -7986,7 +7990,7 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>I. CamaraI. Camara</t>
+          <t>E. HedstromE. Hedstrom</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -8010,7 +8014,7 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>I. HöökI. Höök</t>
+          <t>E. ImeriE. Imeri</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -8034,7 +8038,7 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>J. AzulayJ. Azulay</t>
+          <t>E. LindellE. Lindell</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -8058,7 +8062,7 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>J. KjærJ. Kjær</t>
+          <t>E. Lwampindy BofuaE. Lwampindy Bofua</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -8082,7 +8086,7 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>J. LjungqvistJ. Ljungqvist</t>
+          <t>E. YonanE. Yonan</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -8106,7 +8110,7 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>J. MagnussonJ. Magnusson</t>
+          <t>F. AronssonF. Aronsson</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -8130,7 +8134,7 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>J. MilosavljevicJ. Milosavljevic</t>
+          <t>F. Giuseppe NeatF. Giuseppe Neat</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -8154,7 +8158,7 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>J. NilssonJ. Nilsson</t>
+          <t>F. IhlerF. Ihler</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -8178,7 +8182,7 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>J. PerssonJ. Persson</t>
+          <t>F. NissenF. Nissen</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -8202,7 +8206,7 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>J. TagessonJ. Tagesson</t>
+          <t>F. ÃhmanF. Ãhman</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -8226,7 +8230,7 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>J. WestermarkJ. Westermark</t>
+          <t>F. SchybergF. Schyberg</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -8250,7 +8254,7 @@
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>K. SeverK. Sever</t>
+          <t>G. ErsoyG. Ersoy</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
@@ -8274,7 +8278,7 @@
       <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
-          <t>L. AnderssonL. Andersson</t>
+          <t>G. LajqiG. Lajqi</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -8298,7 +8302,7 @@
       <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
-          <t>L. ArvidssonL. Arvidsson</t>
+          <t>G. LundgrenG. Lundgren</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
@@ -8322,7 +8326,7 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
-          <t>L. HansasL. Hansas</t>
+          <t>H. AtolaH. Atola</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
@@ -8346,7 +8350,7 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>L. HedlundL. Hedlund</t>
+          <t>H. DahlqvistH. Dahlqvist</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
@@ -8370,7 +8374,7 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>L. JäretegL. Järeteg</t>
+          <t>H. KarlssonH. Karlsson</t>
         </is>
       </c>
       <c r="C331" t="inlineStr"/>
@@ -8394,7 +8398,7 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>L. KåhedL. Kåhed</t>
+          <t>I. AdewaleI. Adewale</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
@@ -8418,7 +8422,7 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>L. KyhlénL. Kyhlén</t>
+          <t>I. BuhariI. Buhari</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
@@ -8442,7 +8446,7 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>L. RadakovicL. Radakovic</t>
+          <t>I. HÃ¶Ã¶kI. HÃ¶Ã¶k</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
@@ -8466,7 +8470,7 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>L. RichtnérL. Richtnér</t>
+          <t>J. KjÃ¦rJ. KjÃ¦r</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
@@ -8490,7 +8494,7 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>L. SibeliusL. Sibelius</t>
+          <t>J. MagnussonJ. Magnusson</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
@@ -8514,7 +8518,7 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>L. SvanbergL. Svanberg</t>
+          <t>J. MilosavljevicJ. Milosavljevic</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
@@ -8538,7 +8542,7 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
-          <t>L. VäisänenL. Väisänen</t>
+          <t>J. WestermarkJ. Westermark</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
@@ -8562,7 +8566,7 @@
       <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
-          <t>M. AndersonM. Anderson</t>
+          <t>L. AnderssonL. Andersson</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
@@ -8586,7 +8590,7 @@
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>M. BawaM. Bawa</t>
+          <t>L. HansasL. Hansas</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
@@ -8610,7 +8614,7 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>M. DiabyM. Diaby</t>
+          <t>L. HedlundL. Hedlund</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
@@ -8634,7 +8638,7 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>M. DialloM. Diallo</t>
+          <t>L. JÃ¤retegL. JÃ¤reteg</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
@@ -8658,7 +8662,7 @@
       <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
-          <t>M. EbietomereM. Ebietomere</t>
+          <t>L. KÃ¥hedL. KÃ¥hed</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
@@ -8682,7 +8686,7 @@
       <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
-          <t>M. EllingsenM. Ellingsen</t>
+          <t>L. KyhlÃ©nL. KyhlÃ©n</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
@@ -8706,7 +8710,7 @@
       <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
-          <t>M. IddrisuM. Iddrisu</t>
+          <t>L. RadakovicL. Radakovic</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
@@ -8730,7 +8734,7 @@
       <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
-          <t>M. IsakssonM. Isaksson</t>
+          <t>L. RichtnÃ©rL. RichtnÃ©r</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
@@ -8754,7 +8758,7 @@
       <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
-          <t>M. KamaraM. Kamara</t>
+          <t>L. SibeliusL. Sibelius</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
@@ -8778,7 +8782,7 @@
       <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
-          <t>M. LjungkullM. Ljungkull</t>
+          <t>L. SvanbergL. Svanberg</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
@@ -8802,7 +8806,7 @@
       <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr">
         <is>
-          <t>M. MarquésM. Marqués</t>
+          <t>L. VÃ¤isÃ¤nenL. VÃ¤isÃ¤nen</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
@@ -8826,7 +8830,7 @@
       <c r="A350" t="inlineStr"/>
       <c r="B350" t="inlineStr">
         <is>
-          <t>M. MohamudM. Mohamud</t>
+          <t>M. AndersonM. Anderson</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
@@ -8850,7 +8854,7 @@
       <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
-          <t>M. OlssonM. Olsson</t>
+          <t>M. DiabyM. Diaby</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -8874,7 +8878,7 @@
       <c r="A352" t="inlineStr"/>
       <c r="B352" t="inlineStr">
         <is>
-          <t>M. PålssonM. Pålsson</t>
+          <t>M. DialloM. Diallo</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
@@ -8898,7 +8902,7 @@
       <c r="A353" t="inlineStr"/>
       <c r="B353" t="inlineStr">
         <is>
-          <t>M. SjöblomM. Sjöblom</t>
+          <t>M. EllingsenM. Ellingsen</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
@@ -8922,7 +8926,7 @@
       <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
-          <t>M. StoltM. Stolt</t>
+          <t>M. IddrisuM. Iddrisu</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
@@ -8946,7 +8950,7 @@
       <c r="A355" t="inlineStr"/>
       <c r="B355" t="inlineStr">
         <is>
-          <t>M. ThychosenM. Thychosen</t>
+          <t>M. IsakssonM. Isaksson</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
@@ -8970,7 +8974,7 @@
       <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr">
         <is>
-          <t>M. Vučenović PerssonM. Vučenović Persson</t>
+          <t>M. KamaraM. Kamara</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
@@ -8994,7 +8998,7 @@
       <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Mads HansenMads Hansen</t>
+          <t>M. LjungkullM. Ljungkull</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
@@ -9018,7 +9022,7 @@
       <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Mohamed SoumahMohamed Soumah</t>
+          <t>M. MohamudM. Mohamud</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
@@ -9042,7 +9046,7 @@
       <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>N. MäenpääN. Mäenpää</t>
+          <t>M. OlssonM. Olsson</t>
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
@@ -9066,7 +9070,7 @@
       <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
-          <t>N. MilleskogN. Milleskog</t>
+          <t>M. PÃ¥lssonM. PÃ¥lsson</t>
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
@@ -9090,7 +9094,7 @@
       <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
-          <t>N. StaykovN. Staykov</t>
+          <t>M. SjÃ¶blomM. SjÃ¶blom</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
@@ -9114,7 +9118,7 @@
       <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
-          <t>N. TolfN. Tolf</t>
+          <t>M. StoltM. Stolt</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
@@ -9138,7 +9142,7 @@
       <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
-          <t>N. VasićN. Vasić</t>
+          <t>M. ThychosenM. Thychosen</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
@@ -9162,7 +9166,7 @@
       <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr">
         <is>
-          <t>N. ŽugeljN. Žugelj</t>
+          <t>M. VuÄenoviÄ PerssonM. VuÄenoviÄ Persson</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
@@ -9186,7 +9190,7 @@
       <c r="A365" t="inlineStr"/>
       <c r="B365" t="inlineStr">
         <is>
-          <t>O. CottonO. Cotton</t>
+          <t>Mads HansenMads Hansen</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
@@ -9210,7 +9214,7 @@
       <c r="A366" t="inlineStr"/>
       <c r="B366" t="inlineStr">
         <is>
-          <t>O. HagenO. Hagen</t>
+          <t>N. MÃ¤enpÃ¤Ã¤N. MÃ¤enpÃ¤Ã¤</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
@@ -9234,7 +9238,7 @@
       <c r="A367" t="inlineStr"/>
       <c r="B367" t="inlineStr">
         <is>
-          <t>O. LindbergO. Lindberg</t>
+          <t>N. MilleskogN. Milleskog</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
@@ -9258,7 +9262,7 @@
       <c r="A368" t="inlineStr"/>
       <c r="B368" t="inlineStr">
         <is>
-          <t>O. MånssonO. Månsson</t>
+          <t>N. StaykovN. Staykov</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
@@ -9282,7 +9286,7 @@
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>O. Nilsson LövO. Nilsson Löv</t>
+          <t>N. TolfN. Tolf</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
@@ -9306,7 +9310,7 @@
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>O. SamuelssonO. Samuelsson</t>
+          <t>N. Å½ugeljN. Å½ugelj</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
@@ -9330,7 +9334,7 @@
       <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>P. DahboP. Dahbo</t>
+          <t>O. MÃ¥nssonO. MÃ¥nsson</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
@@ -9354,7 +9358,7 @@
       <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
-          <t>P. GregorP. Gregor</t>
+          <t>O. Nilsson LÃ¶vO. Nilsson LÃ¶v</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
@@ -9378,7 +9382,7 @@
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
-          <t>R. BergvallR. Bergvall</t>
+          <t>O. SamuelssonO. Samuelsson</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
@@ -9402,7 +9406,7 @@
       <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
-          <t>R. LundqvistR. Lundqvist</t>
+          <t>P. DahboP. Dahbo</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
@@ -9426,7 +9430,7 @@
       <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
-          <t>R. ÖrqvistR. Örqvist</t>
+          <t>R. BergvallR. Bergvall</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
@@ -9450,7 +9454,7 @@
       <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
-          <t>R. ThorkelssonR. Thorkelsson</t>
+          <t>R. LundqvistR. Lundqvist</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
@@ -9474,7 +9478,7 @@
       <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr">
         <is>
-          <t>S. GustafssonS. Gustafsson</t>
+          <t>R. ÃrqvistR. Ãrqvist</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
@@ -9498,7 +9502,7 @@
       <c r="A378" t="inlineStr"/>
       <c r="B378" t="inlineStr">
         <is>
-          <t>S. HaaralaS. Haarala</t>
+          <t>S. GustafssonS. Gustafsson</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
@@ -9522,7 +9526,7 @@
       <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
-          <t>S. KondoS. Kondo</t>
+          <t>S. HaaralaS. Haarala</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
@@ -9546,7 +9550,7 @@
       <c r="A380" t="inlineStr"/>
       <c r="B380" t="inlineStr">
         <is>
-          <t>S. OhlssonS. Ohlsson</t>
+          <t>S. KondoS. Kondo</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
@@ -9570,7 +9574,7 @@
       <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
-          <t>S. SandbergS. Sandberg</t>
+          <t>S. OhlssonS. Ohlsson</t>
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
@@ -9594,7 +9598,7 @@
       <c r="A382" t="inlineStr"/>
       <c r="B382" t="inlineStr">
         <is>
-          <t>S. VecchiaS. Vecchia</t>
+          <t>S. SandbergS. Sandberg</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
@@ -9618,7 +9622,7 @@
       <c r="A383" t="inlineStr"/>
       <c r="B383" t="inlineStr">
         <is>
-          <t>S. WändinS. Wändin</t>
+          <t>S. VecchiaS. Vecchia</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
@@ -9642,7 +9646,7 @@
       <c r="A384" t="inlineStr"/>
       <c r="B384" t="inlineStr">
         <is>
-          <t>T. CoimbraT. Coimbra</t>
+          <t>S. WÃ¤ndinS. WÃ¤ndin</t>
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
@@ -9666,7 +9670,7 @@
       <c r="A385" t="inlineStr"/>
       <c r="B385" t="inlineStr">
         <is>
-          <t>T. HelgeT. Helge</t>
+          <t>T. CoimbraT. Coimbra</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
@@ -9690,7 +9694,7 @@
       <c r="A386" t="inlineStr"/>
       <c r="B386" t="inlineStr">
         <is>
-          <t>T. MalmströmT. Malmström</t>
+          <t>T. HelgeT. Helge</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
@@ -9714,7 +9718,7 @@
       <c r="A387" t="inlineStr"/>
       <c r="B387" t="inlineStr">
         <is>
-          <t>T. TekieT. Tekie</t>
+          <t>T. MalmstrÃ¶mT. MalmstrÃ¶m</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
